--- a/server/模板/记事导入模板.xlsx
+++ b/server/模板/记事导入模板.xlsx
@@ -404,7 +404,7 @@
     <col min="3" max="3" width="7.83203125" customWidth="1"/>
     <col min="4" max="4" width="15.33203125" customWidth="1"/>
     <col min="5" max="5" width="19.83203125" customWidth="1"/>
-    <col min="6" max="6" width="25.83203125" customWidth="1"/>
+    <col min="6" max="6" width="19.83203125" customWidth="1"/>
     <col min="7" max="7" width="37.83203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -425,7 +425,7 @@
         <v>优先级(高/中/低)</v>
       </c>
       <c r="F1" t="str">
-        <v>状态(待办/进行中/已完成)</v>
+        <v>状态(待办/已完成)</v>
       </c>
       <c r="G1" t="str">
         <v>提醒时间(YYYY-MM-DD HH:mm)</v>
